--- a/phase3/output/知识图谱节点表.xlsx
+++ b/phase3/output/知识图谱节点表.xlsx
@@ -6329,7 +6329,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N111", "父编码": "N11", "能力层级": "三级", "能力名称": "采集与整理业务数据", "可观察的工作行为": "按指定来源整理数据，保留字段、来源与采集记录", "对应任务ID": "T-JOB002-01;T-JOB007-01;T-JOB013-01;T-JOB022-02", "来源岗位ID": "JOB002;JOB007;JOB013;JOB022", "摘要支持任务ID": "T-JOB002-01;T-JOB007-01;T-JOB013-01;T-JOB022-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "区分人工采集整理与系统数据接入，不能由“整理”推断ETL", "人工审核状态": "待人工审核", "原三级能力编码": "C111", "摘要支持岗位数（含疑似重复）": 4, "摘要支持任务数": 4, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N111", "父编码": "N11", "能力层级": "三级", "能力名称": "采集与整理业务数据", "可观察的工作行为": "按指定来源整理数据，保留字段、来源与采集记录", "对应任务ID": "T-JOB002-01;T-JOB007-01;T-JOB013-01;T-JOB022-02", "来源岗位ID": "JOB002;JOB007;JOB013;JOB022", "摘要支持任务ID": "T-JOB002-01;T-JOB007-01;T-JOB013-01;T-JOB022-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "区分人工采集整理与系统数据接入，不能由“整理”推断ETL", "人工审核状态": "待人工审核", "原三级能力编码": "C111", "摘要支持岗位数（含疑似重复）": 4, "摘要支持任务数": 4, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见可直接对应的采集与来源整理技术任务", "课程尚未明确覆盖的工作行为": "外部业务数据采集、来源记录及整理产出", "未见支撑建议分类": "本课程潜在改进方向", "分类理由": "可讨论来源记录与基础整理案例，是否纳入仍需课程边界论证", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N112", "父编码": "N11", "能力层级": "三级", "能力名称": "接入业务数据", "可观察的工作行为": "识别接入对象与接口，记录数据进入平台的结果", "对应任务ID": "T-JOB035-01", "来源岗位ID": "JOB035", "摘要支持任务ID": "T-JOB035-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "原采集接入含不同操作；仅有接入摘要时支持此项，不据此推定接口技术", "人工审核状态": "待人工审核", "原三级能力编码": "C111", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N112", "父编码": "N11", "能力层级": "三级", "能力名称": "接入业务数据", "可观察的工作行为": "识别接入对象与接口，记录数据进入平台的结果", "对应任务ID": "T-JOB035-01", "来源岗位ID": "JOB035", "摘要支持任务ID": "T-JOB035-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "原采集接入含不同操作；仅有接入摘要时支持此项，不据此推定接口技术", "人工审核状态": "待人工审核", "原三级能力编码": "C111", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见业务数据接入的明确技术任务；数据库连接不等于数据接入", "课程尚未明确覆盖的工作行为": "接口或平台接入、接入结果记录", "未见支撑建议分类": "其他专业课程可能承担", "分类理由": "接入与接口集成可由数据集成类课程讨论；未核查实际开课或承担情况", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N113", "父编码": "N11", "能力层级": "三级", "能力名称": "查询并提取业务数据", "可观察的工作行为": "根据业务问题查询或提取数据并呈现结果；SQL仅在相应证据明确时标注", "对应任务ID": "T-JOB001-02;T-JOB001-04;T-JOB002-03;T-JOB003-02;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB013-02;T-JOB019-01;T-JOB020-01;T-JOB025-01;T-JOB028-01;T-JOB037-01;T-JOB038-01;T-JOB043-01;T-JOB044-01;T-JOB045-01;T-JOB050-01", "来源岗位ID": "JOB001;JOB002;JOB003;JOB006;JOB007;JOB008;JOB009;JOB010;JOB012;JOB013;JOB019;JOB020;JOB025;JOB028;JOB037;JOB038;JOB043;JOB044;JOB045;JOB050", "摘要支持任务ID": "T-JOB001-04;T-JOB003-02;T-JOB012-01;T-JOB025-01;T-JOB038-01;T-JOB044-01;T-JOB050-01", "研究推断任务ID": "T-JOB001-02;T-JOB002-03;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB013-02;T-JOB019-01;T-JOB020-01;T-JOB028-01;T-JOB037-01;T-JOB043-01;T-JOB045-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "合并通用查询与SQL工具条目，保留SQL证据限定，避免同一任务重复计数和把普通分析改称SQL查询", "人工审核状态": "待人工审核", "原三级能力编码": "C113;C131", "摘要支持岗位数（含疑似重复）": 7, "摘要支持任务数": 7, "研究推断关联岗位数（非频次）": 14, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N113", "父编码": "N11", "能力层级": "三级", "能力名称": "查询并提取业务数据", "可观察的工作行为": "根据业务问题查询或提取数据并呈现结果；SQL仅在相应证据明确时标注", "对应任务ID": "T-JOB001-02;T-JOB001-04;T-JOB002-03;T-JOB003-02;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB013-02;T-JOB019-01;T-JOB020-01;T-JOB025-01;T-JOB028-01;T-JOB037-01;T-JOB038-01;T-JOB043-01;T-JOB044-01;T-JOB045-01;T-JOB050-01", "来源岗位ID": "JOB001;JOB002;JOB003;JOB006;JOB007;JOB008;JOB009;JOB010;JOB012;JOB013;JOB019;JOB020;JOB025;JOB028;JOB037;JOB038;JOB043;JOB044;JOB045;JOB050", "摘要支持任务ID": "T-JOB001-04;T-JOB003-02;T-JOB012-01;T-JOB025-01;T-JOB038-01;T-JOB044-01;T-JOB050-01", "研究推断任务ID": "T-JOB001-02;T-JOB002-03;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB013-02;T-JOB019-01;T-JOB020-01;T-JOB028-01;T-JOB037-01;T-JOB043-01;T-JOB045-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "合并通用查询与SQL工具条目，保留SQL证据限定，避免同一任务重复计数和把普通分析改称SQL查询", "人工审核状态": "待人工审核", "原三级能力编码": "C113;C131", "摘要支持岗位数（含疑似重复）": 7, "摘要支持任务数": 7, "研究推断关联岗位数（非频次）": 14, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "按业务场景编写SELECT条件、多表、子查询、分组及视图查询，运行并查看查询结果", "课程尚未明确覆盖的工作行为": "未明确真实旅游业务口径验证、跨系统取数与岗位现场结果交付；这些边界不作为该项已定义查询行为的已确认扩展", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "直接支撑"}</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N121", "父编码": "N12", "能力层级": "三级", "能力名称": "维护指标口径与数据字典", "可观察的工作行为": "说明指标定义、字段含义和计算口径并形成可检查记录", "对应任务ID": "T-JOB003-02;T-JOB011-02", "来源岗位ID": "JOB003;JOB011", "摘要支持任务ID": "T-JOB003-02;T-JOB011-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "指标定义与质量检查评价对象不同；不把“数据治理”自动解释为字典建设", "人工审核状态": "待人工审核", "原三级能力编码": "C121", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N121", "父编码": "N12", "能力层级": "三级", "能力名称": "维护指标口径与数据字典", "可观察的工作行为": "说明指标定义、字段含义和计算口径并形成可检查记录", "对应任务ID": "T-JOB003-02;T-JOB011-02", "来源岗位ID": "JOB003;JOB011", "摘要支持任务ID": "T-JOB003-02;T-JOB011-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "指标定义与质量检查评价对象不同；不把“数据治理”自动解释为字典建设", "人工审核状态": "待人工审核", "原三级能力编码": "C121", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见指标口径或数据字典维护的明确任务", "课程尚未明确覆盖的工作行为": "指标定义、字段含义、计算口径维护及字典记录", "未见支撑建议分类": "本课程潜在改进方向", "分类理由": "可讨论字段与指标字典文档，不宣称原标准已规定", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N122", "父编码": "N12", "能力层级": "三级", "能力名称": "核对与校验业务数据", "可观察的工作行为": "核对来源与汇总结果，标记质量问题及差异", "对应任务ID": "T-JOB011-02;T-JOB033-01", "来源岗位ID": "JOB011;JOB033", "摘要支持任务ID": "T-JOB011-02;T-JOB033-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "将质量核验与口径管理分开；数据链路梳理本身不能证明已经实施质量校验", "人工审核状态": "待人工审核", "原三级能力编码": "C121", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N122", "父编码": "N12", "能力层级": "三级", "能力名称": "核对与校验业务数据", "可观察的工作行为": "核对来源与汇总结果，标记质量问题及差异", "对应任务ID": "T-JOB011-02;T-JOB033-01", "来源岗位ID": "JOB011;JOB033", "摘要支持任务ID": "T-JOB011-02;T-JOB033-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "将质量核验与口径管理分开；数据链路梳理本身不能证明已经实施质量校验", "人工审核状态": "待人工审核", "原三级能力编码": "C121", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "用完整性约束检查数据库记录的规则一致性", "课程尚未明确覆盖的工作行为": "跨来源核对、汇总差异分析及质量问题记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N123", "父编码": "N12", "能力层级": "三级", "能力名称": "维护与更新业务数据", "可观察的工作行为": "按业务规则记录数据维护、更新或同步结果；不预设SQL增删改语法", "对应任务ID": "T-JOB004-01;T-JOB018-01;T-JOB023-03;T-JOB039-01;T-JOB046-01", "来源岗位ID": "JOB004;JOB018;JOB023;JOB039;JOB046", "摘要支持任务ID": "T-JOB039-01;T-JOB046-01", "研究推断任务ID": "T-JOB004-01;T-JOB018-01;T-JOB023-03", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "收窄资源管理为记录维护；宽泛的资源管理不能证明DML或关系数据库设计", "人工审核状态": "待人工审核", "原三级能力编码": "C122", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N123", "父编码": "N12", "能力层级": "三级", "能力名称": "维护与更新业务数据", "可观察的工作行为": "按业务规则记录数据维护、更新或同步结果；不预设SQL增删改语法", "对应任务ID": "T-JOB004-01;T-JOB018-01;T-JOB023-03;T-JOB039-01;T-JOB046-01", "来源岗位ID": "JOB004;JOB018;JOB023;JOB039;JOB046", "摘要支持任务ID": "T-JOB039-01;T-JOB046-01", "研究推断任务ID": "T-JOB004-01;T-JOB018-01;T-JOB023-03", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "收窄资源管理为记录维护；宽泛的资源管理不能证明DML或关系数据库设计", "人工审核状态": "待人工审核", "原三级能力编码": "C122", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "用条件更新和视图操作维护数据库记录", "课程尚未明确覆盖的工作行为": "平台业务规则落实、跨系统同步及完整业务维护结果记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N124", "父编码": "N12", "能力层级": "三级", "能力名称": "组织会员标签与画像", "可观察的工作行为": "按会员业务对象整理标签及画像结果并说明含义", "对应任务ID": "T-JOB001-01;T-JOB001-03;T-JOB046-01", "来源岗位ID": "JOB001;JOB046", "摘要支持任务ID": "T-JOB001-01;T-JOB001-03;T-JOB046-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留旅游会员场景；业务标签体系不等同于数据库表结构", "人工审核状态": "待人工审核", "原三级能力编码": "C123", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N124", "父编码": "N12", "能力层级": "三级", "能力名称": "组织会员标签与画像", "可观察的工作行为": "按会员业务对象整理标签及画像结果并说明含义", "对应任务ID": "T-JOB001-01;T-JOB001-03;T-JOB046-01", "来源岗位ID": "JOB001;JOB046", "摘要支持任务ID": "T-JOB001-01;T-JOB001-03;T-JOB046-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留旅游会员场景；业务标签体系不等同于数据库表结构", "人工审核状态": "待人工审核", "原三级能力编码": "C123", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见会员标签或画像制作任务；E-R设计不能替代画像方法", "课程尚未明确覆盖的工作行为": "会员业务标签组织、画像含义及结果说明", "未见支撑建议分类": "其他专业课程可能承担", "分类理由": "会员画像方法可能涉及用户分析等课程；不是实际课程承担证明", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N125", "父编码": "N12", "能力层级": "三级", "能力名称": "清洗与标准化业务数据", "可观察的工作行为": "识别缺失、异常和格式差异，形成清洗结果与处理说明", "对应任务ID": "T-JOB002-02;T-JOB012-01;T-JOB013-01;T-JOB013-03;T-JOB046-01;T-JOB048-01", "来源岗位ID": "JOB002;JOB012;JOB013;JOB046;JOB048", "摘要支持任务ID": "T-JOB002-02;T-JOB012-01;T-JOB013-01;T-JOB013-03;T-JOB046-01;T-JOB048-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "规范名称与评价产物；不预设必须在数据库内实施清洗", "人工审核状态": "待人工审核", "原三级能力编码": "C112", "摘要支持岗位数（含疑似重复）": 5, "摘要支持任务数": 6, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N125", "父编码": "N12", "能力层级": "三级", "能力名称": "清洗与标准化业务数据", "可观察的工作行为": "识别缺失、异常和格式差异，形成清洗结果与处理说明", "对应任务ID": "T-JOB002-02;T-JOB012-01;T-JOB013-01;T-JOB013-03;T-JOB046-01;T-JOB048-01", "来源岗位ID": "JOB002;JOB012;JOB013;JOB046;JOB048", "摘要支持任务ID": "T-JOB002-02;T-JOB012-01;T-JOB013-01;T-JOB013-03;T-JOB046-01;T-JOB048-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "规范名称与评价产物；不预设必须在数据库内实施清洗", "人工审核状态": "待人工审核", "原三级能力编码": "C112", "摘要支持岗位数（含疑似重复）": 5, "摘要支持任务数": 6, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "用约束和条件更新支持部分数据规则一致性处理", "课程尚未明确覆盖的工作行为": "缺失异常识别、格式标准化、清洗过程与结果说明", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr"/>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N211", "父编码": "N21", "能力层级": "三级", "能力名称": "构建业务指标体系", "可观察的工作行为": "列出指标对象、定义与业务用途，形成指标结构", "对应任务ID": "T-JOB009-02;T-JOB010-01;T-JOB011-01;T-JOB011-02;T-JOB013-02;T-JOB043-01;T-JOB047-01", "来源岗位ID": "JOB009;JOB010;JOB011;JOB013;JOB043;JOB047", "摘要支持任务ID": "T-JOB009-02;T-JOB010-01;T-JOB011-01;T-JOB013-02", "研究推断任务ID": "T-JOB011-02;T-JOB043-01;T-JOB047-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "构建与日常统计监测属于不同工作行为；不能由“统计”推断指标体系设计", "人工审核状态": "待人工审核", "原三级能力编码": "C211", "摘要支持岗位数（含疑似重复）": 4, "摘要支持任务数": 4, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N211", "父编码": "N21", "能力层级": "三级", "能力名称": "构建业务指标体系", "可观察的工作行为": "列出指标对象、定义与业务用途，形成指标结构", "对应任务ID": "T-JOB009-02;T-JOB010-01;T-JOB011-01;T-JOB011-02;T-JOB013-02;T-JOB043-01;T-JOB047-01", "来源岗位ID": "JOB009;JOB010;JOB011;JOB013;JOB043;JOB047", "摘要支持任务ID": "T-JOB009-02;T-JOB010-01;T-JOB011-01;T-JOB013-02", "研究推断任务ID": "T-JOB011-02;T-JOB043-01;T-JOB047-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "构建与日常统计监测属于不同工作行为；不能由“统计”推断指标体系设计", "人工审核状态": "待人工审核", "原三级能力编码": "C211", "摘要支持岗位数（含疑似重复）": 4, "摘要支持任务数": 4, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "聚合函数与分组统计完成指标计算子环节", "课程尚未明确覆盖的工作行为": "指标业务定义、用途分析和指标体系结构设计", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N212", "父编码": "N21", "能力层级": "三级", "能力名称": "统计与监测业务指标", "可观察的工作行为": "按既定指标统计结果并标记变化或异常", "对应任务ID": "T-JOB003-01;T-JOB004-01;T-JOB005-01;T-JOB005-02;T-JOB011-02;T-JOB014-02;T-JOB018-01;T-JOB022-01;T-JOB023-02;T-JOB026-01;T-JOB027-01;T-JOB030-01;T-JOB031-01;T-JOB036-01;T-JOB038-01;T-JOB043-01;T-JOB047-01;T-JOB048-01", "来源岗位ID": "JOB003;JOB004;JOB005;JOB011;JOB014;JOB018;JOB022;JOB023;JOB026;JOB027;JOB030;JOB031;JOB036;JOB038;JOB043;JOB047;JOB048", "摘要支持任务ID": "T-JOB003-01;T-JOB004-01;T-JOB005-01;T-JOB005-02;T-JOB014-02;T-JOB018-01;T-JOB022-01;T-JOB023-02;T-JOB026-01;T-JOB027-01;T-JOB030-01;T-JOB031-01;T-JOB036-01;T-JOB038-01;T-JOB048-01", "研究推断任务ID": "T-JOB011-02;T-JOB043-01;T-JOB047-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "统计与监测保留为执行层面，不推断SQL聚合、分组或统计检验方法", "人工审核状态": "待人工审核", "原三级能力编码": "C211", "摘要支持岗位数（含疑似重复）": 14, "摘要支持任务数": 15, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N212", "父编码": "N21", "能力层级": "三级", "能力名称": "统计与监测业务指标", "可观察的工作行为": "按既定指标统计结果并标记变化或异常", "对应任务ID": "T-JOB003-01;T-JOB004-01;T-JOB005-01;T-JOB005-02;T-JOB011-02;T-JOB014-02;T-JOB018-01;T-JOB022-01;T-JOB023-02;T-JOB026-01;T-JOB027-01;T-JOB030-01;T-JOB031-01;T-JOB036-01;T-JOB038-01;T-JOB043-01;T-JOB047-01;T-JOB048-01", "来源岗位ID": "JOB003;JOB004;JOB005;JOB011;JOB014;JOB018;JOB022;JOB023;JOB026;JOB027;JOB030;JOB031;JOB036;JOB038;JOB043;JOB047;JOB048", "摘要支持任务ID": "T-JOB003-01;T-JOB004-01;T-JOB005-01;T-JOB005-02;T-JOB014-02;T-JOB018-01;T-JOB022-01;T-JOB023-02;T-JOB026-01;T-JOB027-01;T-JOB030-01;T-JOB031-01;T-JOB036-01;T-JOB038-01;T-JOB048-01", "研究推断任务ID": "T-JOB011-02;T-JOB043-01;T-JOB047-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "统计与监测保留为执行层面，不推断SQL聚合、分组或统计检验方法", "人工审核状态": "待人工审核", "原三级能力编码": "C211", "摘要支持岗位数（含疑似重复）": 14, "摘要支持任务数": 15, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "查询与分组统计形成统计结果", "课程尚未明确覆盖的工作行为": "持续监测过程、变化或异常标记及业务记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N213", "父编码": "N21", "能力层级": "三级", "能力名称": "分析旅游经营数据", "可观察的工作行为": "围绕明确业务问题解释数据变化，形成有依据的分析结果", "对应任务ID": "T-JOB001-02;T-JOB001-04;T-JOB002-03;T-JOB004-01;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB012-03;T-JOB013-02;T-JOB014-02;T-JOB015-01;T-JOB016-02;T-JOB018-01;T-JOB019-01;T-JOB020-01;T-JOB023-01;T-JOB028-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB033-01;T-JOB034-01;T-JOB035-01;T-JOB036-01;T-JOB037-01;T-JOB038-01;T-JOB041-01;T-JOB043-01;T-JOB044-01;T-JOB045-01;T-JOB047-01", "来源岗位ID": "JOB001;JOB002;JOB004;JOB006;JOB007;JOB008;JOB009;JOB010;JOB012;JOB013;JOB014;JOB015;JOB016;JOB018;JOB019;JOB020;JOB023;JOB028;JOB029;JOB030;JOB031;JOB033;JOB034;JOB035;JOB036;JOB037;JOB038;JOB041;JOB043;JOB044;JOB045;JOB047", "摘要支持任务ID": "T-JOB001-02;T-JOB001-04;T-JOB004-01;T-JOB006-01;T-JOB007-01;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB012-03;T-JOB014-02;T-JOB015-01;T-JOB018-01;T-JOB019-01;T-JOB020-01;T-JOB023-01;T-JOB028-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB033-01;T-JOB034-01;T-JOB035-01;T-JOB036-01;T-JOB043-01;T-JOB044-01;T-JOB045-01", "研究推断任务ID": "T-JOB002-03;T-JOB007-03;T-JOB013-02;T-JOB016-02;T-JOB037-01;T-JOB038-01;T-JOB041-01;T-JOB047-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "限定业务对象；单一“分析”不能证明统计方法、数据库操作或模型设计", "人工审核状态": "待人工审核", "原三级能力编码": "C212", "摘要支持岗位数（含疑似重复）": 25, "摘要支持任务数": 27, "研究推断关联岗位数（非频次）": 8, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N213", "父编码": "N21", "能力层级": "三级", "能力名称": "分析旅游经营数据", "可观察的工作行为": "围绕明确业务问题解释数据变化，形成有依据的分析结果", "对应任务ID": "T-JOB001-02;T-JOB001-04;T-JOB002-03;T-JOB004-01;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB012-03;T-JOB013-02;T-JOB014-02;T-JOB015-01;T-JOB016-02;T-JOB018-01;T-JOB019-01;T-JOB020-01;T-JOB023-01;T-JOB028-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB033-01;T-JOB034-01;T-JOB035-01;T-JOB036-01;T-JOB037-01;T-JOB038-01;T-JOB041-01;T-JOB043-01;T-JOB044-01;T-JOB045-01;T-JOB047-01", "来源岗位ID": "JOB001;JOB002;JOB004;JOB006;JOB007;JOB008;JOB009;JOB010;JOB012;JOB013;JOB014;JOB015;JOB016;JOB018;JOB019;JOB020;JOB023;JOB028;JOB029;JOB030;JOB031;JOB033;JOB034;JOB035;JOB036;JOB037;JOB038;JOB041;JOB043;JOB044;JOB045;JOB047", "摘要支持任务ID": "T-JOB001-02;T-JOB001-04;T-JOB004-01;T-JOB006-01;T-JOB007-01;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB012-03;T-JOB014-02;T-JOB015-01;T-JOB018-01;T-JOB019-01;T-JOB020-01;T-JOB023-01;T-JOB028-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB033-01;T-JOB034-01;T-JOB035-01;T-JOB036-01;T-JOB043-01;T-JOB044-01;T-JOB045-01", "研究推断任务ID": "T-JOB002-03;T-JOB007-03;T-JOB013-02;T-JOB016-02;T-JOB037-01;T-JOB038-01;T-JOB041-01;T-JOB047-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "限定业务对象；单一“分析”不能证明统计方法、数据库操作或模型设计", "人工审核状态": "待人工审核", "原三级能力编码": "C212", "摘要支持岗位数（含疑似重复）": 25, "摘要支持任务数": 27, "研究推断关联岗位数（非频次）": 8, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "查询与汇总提供业务分析所需的部分数据结果", "课程尚未明确覆盖的工作行为": "围绕旅游经营问题作解释、归因并形成分析成果", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N221", "父编码": "N22", "能力层级": "三级", "能力名称": "构建数据分析模型", "可观察的工作行为": "说明分析对象、输入与模型用途并给出分析模型结果", "对应任务ID": "T-JOB013-02;T-JOB048-01", "来源岗位ID": "JOB013;JOB048", "摘要支持任务ID": "T-JOB013-02;T-JOB048-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "数据分析模型与预测模型分开；不把一般建模解释为实体关系设计", "人工审核状态": "待人工审核", "原三级能力编码": "C231", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N221", "父编码": "N22", "能力层级": "三级", "能力名称": "构建数据分析模型", "可观察的工作行为": "说明分析对象、输入与模型用途并给出分析模型结果", "对应任务ID": "T-JOB013-02;T-JOB048-01", "来源岗位ID": "JOB013;JOB048", "摘要支持任务ID": "T-JOB013-02;T-JOB048-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "数据分析模型与预测模型分开；不把一般建模解释为实体关系设计", "人工审核状态": "待人工审核", "原三级能力编码": "C231", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见明确数据分析模型训练；E-R模型属于数据库结构设计", "课程尚未明确覆盖的工作行为": "岗位所称分析模型的对象、输入、用途及模型结果仍需招聘原文澄清", "未见支撑建议分类": "证据不足无法判断", "分类理由": "既有摘要中的分析模型对象不明确，在当前证据范围无法判断；不新增招聘核验任务。", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N222", "父编码": "N22", "能力层级": "三级", "能力名称": "构建业务预测模型", "可观察的工作行为": "说明预测对象、输入和预测结果的用途", "对应任务ID": "T-JOB037-01", "来源岗位ID": "JOB037", "摘要支持任务ID": "T-JOB037-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "只在摘要出现预测任务时支持；不增加具体算法需求", "人工审核状态": "待人工审核", "原三级能力编码": "C231", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N222", "父编码": "N22", "能力层级": "三级", "能力名称": "构建业务预测模型", "可观察的工作行为": "说明预测对象、输入和预测结果的用途", "对应任务ID": "T-JOB037-01", "来源岗位ID": "JOB037", "摘要支持任务ID": "T-JOB037-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "只在摘要出现预测任务时支持；不增加具体算法需求", "人工审核状态": "待人工审核", "原三级能力编码": "C231", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见业务预测模型的明确教学技术任务", "课程尚未明确覆盖的工作行为": "预测对象、模型输入、预测结果及用途说明", "未见支撑建议分类": "其他专业课程可能承担", "分类理由": "预测建模可能由分析建模类课程讨论，未证实实际课程设置", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N223", "父编码": "N22", "能力层级": "三级", "能力名称": "提出经营改进建议", "可观察的工作行为": "依据分析结果提出成本、收益或运营建议并说明依据", "对应任务ID": "T-JOB006-01;T-JOB009-01;T-JOB019-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB034-01;T-JOB040-01;T-JOB042-01;T-JOB047-01", "来源岗位ID": "JOB006;JOB009;JOB019;JOB029;JOB030;JOB031;JOB034;JOB040;JOB042;JOB047", "摘要支持任务ID": "T-JOB006-01;T-JOB009-01;T-JOB019-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB034-01;T-JOB042-01;T-JOB047-01", "研究推断任务ID": "T-JOB040-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留建议产出，与实际执行增长改进区分；不把流程优化泛化为经营策略", "人工审核状态": "待人工审核", "原三级能力编码": "C232", "摘要支持岗位数（含疑似重复）": 9, "摘要支持任务数": 9, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N223", "父编码": "N22", "能力层级": "三级", "能力名称": "提出经营改进建议", "可观察的工作行为": "依据分析结果提出成本、收益或运营建议并说明依据", "对应任务ID": "T-JOB006-01;T-JOB009-01;T-JOB019-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB034-01;T-JOB040-01;T-JOB042-01;T-JOB047-01", "来源岗位ID": "JOB006;JOB009;JOB019;JOB029;JOB030;JOB031;JOB034;JOB040;JOB042;JOB047", "摘要支持任务ID": "T-JOB006-01;T-JOB009-01;T-JOB019-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB034-01;T-JOB042-01;T-JOB047-01", "研究推断任务ID": "T-JOB040-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留建议产出，与实际执行增长改进区分；不把流程优化泛化为经营策略", "人工审核状态": "待人工审核", "原三级能力编码": "C232", "摘要支持岗位数（含疑似重复）": 9, "摘要支持任务数": 9, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见经营改进建议形成的明确技术任务", "课程尚未明确覆盖的工作行为": "依据分析提出成本收益或运营建议并说明依据", "未见支撑建议分类": "旅游业务背景能力", "分类理由": "经营建议属于业务决策情境，不应强行扩为数据库核心内容", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N224", "父编码": "N22", "能力层级": "三级", "能力名称": "实施业务增长改进", "可观察的工作行为": "围绕转化或增长目标记录运营改进行动及结果", "对应任务ID": "T-JOB015-02", "来源岗位ID": "JOB015", "摘要支持任务ID": "T-JOB015-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留执行行为，与建议形成区分，虽相关但不直接合并", "人工审核状态": "待人工审核", "原三级能力编码": "C233", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N224", "父编码": "N22", "能力层级": "三级", "能力名称": "实施业务增长改进", "可观察的工作行为": "围绕转化或增长目标记录运营改进行动及结果", "对应任务ID": "T-JOB015-02", "来源岗位ID": "JOB015", "摘要支持任务ID": "T-JOB015-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留执行行为，与建议形成区分，虽相关但不直接合并", "人工审核状态": "待人工审核", "原三级能力编码": "C233", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见转化或增长改进行动的明确技术任务", "课程尚未明确覆盖的工作行为": "执行运营改进行动并记录增长或转化结果", "未见支撑建议分类": "旅游业务背景能力", "分类理由": "增长执行属于旅游业务运营情境，需专业层面讨论", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr"/>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N231", "父编码": "N23", "能力层级": "三级", "能力名称": "编制业务统计报表与报告", "可观察的工作行为": "依据业务数据形成报表或报告，标注统计口径和来源", "对应任务ID": "T-JOB002-03;T-JOB003-02;T-JOB007-03;T-JOB014-02;T-JOB018-01;T-JOB020-01;T-JOB022-02;T-JOB023-02;T-JOB035-01;T-JOB037-01;T-JOB043-01;T-JOB049-02", "来源岗位ID": "JOB002;JOB003;JOB007;JOB014;JOB018;JOB020;JOB022;JOB023;JOB035;JOB037;JOB043;JOB049", "摘要支持任务ID": "T-JOB002-03;T-JOB003-02;T-JOB007-03;T-JOB014-02;T-JOB018-01;T-JOB020-01;T-JOB022-02;T-JOB023-02;T-JOB035-01;T-JOB037-01;T-JOB043-01;T-JOB049-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "报表报告与交互看板分开评价，不能由“报告”推断可视化工具", "人工审核状态": "待人工审核", "原三级能力编码": "C221", "摘要支持岗位数（含疑似重复）": 12, "摘要支持任务数": 12, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N231", "父编码": "N23", "能力层级": "三级", "能力名称": "编制业务统计报表与报告", "可观察的工作行为": "依据业务数据形成报表或报告，标注统计口径和来源", "对应任务ID": "T-JOB002-03;T-JOB003-02;T-JOB007-03;T-JOB014-02;T-JOB018-01;T-JOB020-01;T-JOB022-02;T-JOB023-02;T-JOB035-01;T-JOB037-01;T-JOB043-01;T-JOB049-02", "来源岗位ID": "JOB002;JOB003;JOB007;JOB014;JOB018;JOB020;JOB022;JOB023;JOB035;JOB037;JOB043;JOB049", "摘要支持任务ID": "T-JOB002-03;T-JOB003-02;T-JOB007-03;T-JOB014-02;T-JOB018-01;T-JOB020-01;T-JOB022-02;T-JOB023-02;T-JOB035-01;T-JOB037-01;T-JOB043-01;T-JOB049-02", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "报表报告与交互看板分开评价，不能由“报告”推断可视化工具", "人工审核状态": "待人工审核", "原三级能力编码": "C221", "摘要支持岗位数（含疑似重复）": 12, "摘要支持任务数": 12, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见报表报告编制规范；查询结果集不等于报表成果", "课程尚未明确覆盖的工作行为": "报表报告编制、口径来源标注与可检查文档产出", "未见支撑建议分类": "本课程潜在改进方向", "分类理由": "可讨论查询结果的基础报表交付，但须审批任务及评价要求", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N232", "父编码": "N23", "能力层级": "三级", "能力名称": "制作业务可视化看板", "可观察的工作行为": "将业务指标呈现为看板或可视化结果并解释含义", "对应任务ID": "T-JOB003-02;T-JOB012-02;T-JOB013-03;T-JOB036-01;T-JOB038-01;T-JOB048-01", "来源岗位ID": "JOB003;JOB012;JOB013;JOB036;JOB038;JOB048", "摘要支持任务ID": "T-JOB003-02;T-JOB012-02;T-JOB013-03;T-JOB036-01;T-JOB038-01;T-JOB048-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "只有看板或可视化摘要支持；大屏运维不等于可视化开发", "人工审核状态": "待人工审核", "原三级能力编码": "C221", "摘要支持岗位数（含疑似重复）": 6, "摘要支持任务数": 6, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N232", "父编码": "N23", "能力层级": "三级", "能力名称": "制作业务可视化看板", "可观察的工作行为": "将业务指标呈现为看板或可视化结果并解释含义", "对应任务ID": "T-JOB003-02;T-JOB012-02;T-JOB013-03;T-JOB036-01;T-JOB038-01;T-JOB048-01", "来源岗位ID": "JOB003;JOB012;JOB013;JOB036;JOB038;JOB048", "摘要支持任务ID": "T-JOB003-02;T-JOB012-02;T-JOB013-03;T-JOB036-01;T-JOB038-01;T-JOB048-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "只有看板或可视化摘要支持；大屏运维不等于可视化开发", "人工审核状态": "待人工审核", "原三级能力编码": "C221", "摘要支持岗位数（含疑似重复）": 6, "摘要支持任务数": 6, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见业务可视化看板制作任务；数据库GUI不是业务看板", "课程尚未明确覆盖的工作行为": "业务指标可视化呈现、看板制作及含义说明", "未见支撑建议分类": "其他专业课程可能承担", "分类理由": "业务看板可由可视化类课程讨论，不等于已由其他课程覆盖", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N311", "父编码": "N31", "能力层级": "三级", "能力名称": "维护与配置旅游业务系统", "可观察的工作行为": "记录业务系统配置、巡检或维护的对象及结果", "对应任务ID": "T-JOB001-03;T-JOB005-01;T-JOB008-02;T-JOB017-01;T-JOB020-01;T-JOB021-01;T-JOB021-02;T-JOB022-01;T-JOB024-01;T-JOB025-01;T-JOB027-01;T-JOB033-01;T-JOB035-01;T-JOB039-01;T-JOB049-01", "来源岗位ID": "JOB001;JOB005;JOB008;JOB017;JOB020;JOB021;JOB022;JOB024;JOB025;JOB027;JOB033;JOB035;JOB039;JOB049", "摘要支持任务ID": "T-JOB001-03;T-JOB005-01;T-JOB008-02;T-JOB020-01;T-JOB021-01;T-JOB022-01;T-JOB024-01;T-JOB025-01;T-JOB027-01;T-JOB033-01;T-JOB035-01;T-JOB049-01", "研究推断任务ID": "T-JOB017-01;T-JOB021-02;T-JOB039-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "普通系统运维与数据库运维分层说明；仅数据库日常运维不自动支持一般业务系统配置", "人工审核状态": "待人工审核", "原三级能力编码": "C311", "摘要支持岗位数（含疑似重复）": 12, "摘要支持任务数": 12, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N311", "父编码": "N31", "能力层级": "三级", "能力名称": "维护与配置旅游业务系统", "可观察的工作行为": "记录业务系统配置、巡检或维护的对象及结果", "对应任务ID": "T-JOB001-03;T-JOB005-01;T-JOB008-02;T-JOB017-01;T-JOB020-01;T-JOB021-01;T-JOB021-02;T-JOB022-01;T-JOB024-01;T-JOB025-01;T-JOB027-01;T-JOB033-01;T-JOB035-01;T-JOB039-01;T-JOB049-01", "来源岗位ID": "JOB001;JOB005;JOB008;JOB017;JOB020;JOB021;JOB022;JOB024;JOB025;JOB027;JOB033;JOB035;JOB039;JOB049", "摘要支持任务ID": "T-JOB001-03;T-JOB005-01;T-JOB008-02;T-JOB020-01;T-JOB021-01;T-JOB022-01;T-JOB024-01;T-JOB025-01;T-JOB027-01;T-JOB033-01;T-JOB035-01;T-JOB049-01", "研究推断任务ID": "T-JOB017-01;T-JOB021-02;T-JOB039-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "普通系统运维与数据库运维分层说明；仅数据库日常运维不自动支持一般业务系统配置", "人工审核状态": "待人工审核", "原三级能力编码": "C311", "摘要支持岗位数（含疑似重复）": 12, "摘要支持任务数": 12, "研究推断关联岗位数（非频次）": 3, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "MySQL环境安装配置与连接", "课程尚未明确覆盖的工作行为": "旅游业务系统的日常维护、配置变更和维护结果记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N312", "父编码": "N31", "能力层级": "三级", "能力名称": "排查业务系统故障", "可观察的工作行为": "记录故障现象、定位过程及处理结果", "对应任务ID": "T-JOB017-01;T-JOB024-02;T-JOB032-01", "来源岗位ID": "JOB017;JOB024;JOB032", "摘要支持任务ID": "T-JOB017-01;T-JOB024-02;T-JOB032-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留通用故障处理，未确认数据库对象前不改称数据库故障处理", "人工审核状态": "待人工审核", "原三级能力编码": "C312", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N312", "父编码": "N31", "能力层级": "三级", "能力名称": "排查业务系统故障", "可观察的工作行为": "记录故障现象、定位过程及处理结果", "对应任务ID": "T-JOB017-01;T-JOB024-02;T-JOB032-01", "来源岗位ID": "JOB017;JOB024;JOB032", "摘要支持任务ID": "T-JOB017-01;T-JOB024-02;T-JOB032-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留通用故障处理，未确认数据库对象前不改称数据库故障处理", "人工审核状态": "待人工审核", "原三级能力编码": "C312", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "MySQL安装中的环境错误排查与连接问题处理基础", "课程尚未明确覆盖的工作行为": "其他业务系统故障定位、完整处理过程及结果记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N313", "父编码": "N31", "能力层级": "三级", "能力名称": "执行数据库运行维护", "可观察的工作行为": "明确数据库或数据库应用系统对象，记录运行维护操作结果", "对应任务ID": "T-JOB021-01;T-JOB026-01", "来源岗位ID": "JOB021;JOB026", "摘要支持任务ID": "T-JOB021-01;T-JOB026-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "收窄数据库管理为运行维护；与一般系统维护分开，具体数据库操作仍待核验", "人工审核状态": "待人工审核", "原三级能力编码": "C321", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N313", "父编码": "N31", "能力层级": "三级", "能力名称": "执行数据库运行维护", "可观察的工作行为": "明确数据库或数据库应用系统对象，记录运行维护操作结果", "对应任务ID": "T-JOB021-01;T-JOB026-01", "来源岗位ID": "JOB021;JOB026", "摘要支持任务ID": "T-JOB021-01;T-JOB026-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "收窄数据库管理为运行维护；与一般系统维护分开，具体数据库操作仍待核验", "人工审核状态": "待人工审核", "原三级能力编码": "C321", "摘要支持岗位数（含疑似重复）": 2, "摘要支持任务数": 2, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "MySQL安装连接、视图索引操作及数据库备份恢复的基础操作", "课程尚未明确覆盖的工作行为": "数据库或数据库应用系统运行维护对象的完整界定、连续工作过程及维护操作结果记录；课标未明确形成完整运维工作产出", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr"/>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N321", "父编码": "N32", "能力层级": "三级", "能力名称": "执行业务数据备份", "可观察的工作行为": "明确备份对象，执行备份并记录备份产物", "对应任务ID": "T-JOB005-03;T-JOB017-01;T-JOB025-01;T-JOB027-01;T-JOB032-01", "来源岗位ID": "JOB005;JOB017;JOB025;JOB027;JOB032", "摘要支持任务ID": "T-JOB005-03;T-JOB025-01;T-JOB027-01;T-JOB032-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "备份与恢复可分别评价；对象未明确为数据库时不得宣称数据库备份需求", "人工审核状态": "待人工审核", "原三级能力编码": "C331", "摘要支持岗位数（含疑似重复）": 4, "摘要支持任务数": 4, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N321", "父编码": "N32", "能力层级": "三级", "能力名称": "执行业务数据备份", "可观察的工作行为": "明确备份对象，执行备份并记录备份产物", "对应任务ID": "T-JOB005-03;T-JOB017-01;T-JOB025-01;T-JOB027-01;T-JOB032-01", "来源岗位ID": "JOB005;JOB017;JOB025;JOB027;JOB032", "摘要支持任务ID": "T-JOB005-03;T-JOB025-01;T-JOB027-01;T-JOB032-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "备份与恢复可分别评价；对象未明确为数据库时不得宣称数据库备份需求", "人工审核状态": "待人工审核", "原三级能力编码": "C331", "摘要支持岗位数（含疑似重复）": 4, "摘要支持任务数": 4, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "数据库工具或命令的基本备份流程与独立备份实操", "课程尚未明确覆盖的工作行为": "备份对象的业务范围确认及备份产物记录要求；不能把数据库备份实验扩大为全部业务数据备份工作", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N322", "父编码": "N32", "能力层级": "三级", "能力名称": "恢复业务数据", "可观察的工作行为": "依据恢复任务实施恢复并记录结果", "对应任务ID": "T-JOB017-01;T-JOB032-01", "来源岗位ID": "JOB017;JOB032", "摘要支持任务ID": "T-JOB032-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "不能从有备份推断恢复要求；只在恢复摘要出现时支持", "人工审核状态": "待人工审核", "原三级能力编码": "C331", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N322", "父编码": "N32", "能力层级": "三级", "能力名称": "恢复业务数据", "可观察的工作行为": "依据恢复任务实施恢复并记录结果", "对应任务ID": "T-JOB017-01;T-JOB032-01", "来源岗位ID": "JOB017;JOB032", "摘要支持任务ID": "T-JOB032-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "不能从有备份推断恢复要求；只在恢复摘要出现时支持", "人工审核状态": "待人工审核", "原三级能力编码": "C331", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "数据库基本恢复流程和备份恢复实操", "课程尚未明确覆盖的工作行为": "依据具体业务恢复任务确定对象、实施恢复并形成结果记录的完整要求；不能从恢复实验推定完整业务恢复行为", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N331", "父编码": "N33", "能力层级": "三级", "能力名称": "配置与维护访问权限", "可观察的工作行为": "说明访问对象、权限配置及变更结果", "对应任务ID": "T-JOB005-03;T-JOB025-01;T-JOB027-01", "来源岗位ID": "JOB005;JOB025;JOB027", "摘要支持任务ID": "T-JOB005-03;T-JOB025-01;T-JOB027-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "拆分访问授权与安全审计；应用权限不自动等于数据库GRANT或REVOKE需求", "人工审核状态": "待人工审核", "原三级能力编码": "C332", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N331", "父编码": "N33", "能力层级": "三级", "能力名称": "配置与维护访问权限", "可观察的工作行为": "说明访问对象、权限配置及变更结果", "对应任务ID": "T-JOB005-03;T-JOB025-01;T-JOB027-01", "来源岗位ID": "JOB005;JOB025;JOB027", "摘要支持任务ID": "T-JOB005-03;T-JOB025-01;T-JOB027-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "拆分访问授权与安全审计；应用权限不自动等于数据库GRANT或REVOKE需求", "人工审核状态": "待人工审核", "原三级能力编码": "C332", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "目标层提出权限管理和DCL基础", "课程尚未明确覆盖的工作行为": "访问对象确认、具体权限配置变更与结果记录；未明确对应授权实操", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr"/>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N332", "父编码": "N33", "能力层级": "三级", "能力名称": "执行系统安全检查与审计", "可观察的工作行为": "按任务检查安全或审计记录并记录问题", "对应任务ID": "T-JOB017-01", "来源岗位ID": "JOB017", "摘要支持任务ID": "T-JOB017-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留安全检查对象和记录；不从系统安全推断数据库安全技术细节", "人工审核状态": "待人工审核", "原三级能力编码": "C332", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N332", "父编码": "N33", "能力层级": "三级", "能力名称": "执行系统安全检查与审计", "可观察的工作行为": "按任务检查安全或审计记录并记录问题", "对应任务ID": "T-JOB017-01", "来源岗位ID": "JOB017", "摘要支持任务ID": "T-JOB017-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留安全检查对象和记录；不从系统安全推断数据库安全技术细节", "人工审核状态": "待人工审核", "原三级能力编码": "C332", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "思政段落提及用户权限、加密与审计，尚不能确认技术训练", "课程尚未明确覆盖的工作行为": "安全检查步骤、审计记录核查与问题记录的技术任务和评价要求", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "待人工审核"}</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N341", "父编码": "N34", "能力层级": "三级", "能力名称": "优化数据库查询性能", "可观察的工作行为": "围绕数据库查询说明性能问题、优化操作及结果", "对应任务ID": "T-JOB050-01", "来源岗位ID": "JOB050", "摘要支持任务ID": "T-JOB050-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "从系统建设调整至运行优化；不增加索引或执行计划等未出现的具体招聘要求", "人工审核状态": "待人工审核", "原三级能力编码": "C421", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N341", "父编码": "N34", "能力层级": "三级", "能力名称": "优化数据库查询性能", "可观察的工作行为": "围绕数据库查询说明性能问题、优化操作及结果", "对应任务ID": "T-JOB050-01", "来源岗位ID": "JOB050", "摘要支持任务ID": "T-JOB050-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "A数据库课程核心相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "从系统建设调整至运行优化；不增加索引或执行计划等未出现的具体招聘要求", "人工审核状态": "待人工审核", "原三级能力编码": "C421", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "索引创建删除与维护、比较有无索引的查询效果", "课程尚未明确覆盖的工作行为": "围绕具体查询性能问题说明优化操作及优化结果的完整工作产出；课标明确的是索引技术与效果对比，不是所有查询性能优化工作", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N411", "父编码": "N41", "能力层级": "三级", "能力名称": "梳理业务系统需求", "可观察的工作行为": "整理业务场景、功能需求及约束并形成需求记录", "对应任务ID": "T-JOB016-01;T-JOB032-01;T-JOB045-01", "来源岗位ID": "JOB016;JOB032;JOB045", "摘要支持任务ID": "T-JOB016-01;T-JOB032-01;T-JOB045-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "限定系统需求；市场需求调研或一般分析不能自动归入系统需求", "人工审核状态": "待人工审核", "原三级能力编码": "C411", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N411", "父编码": "N41", "能力层级": "三级", "能力名称": "梳理业务系统需求", "可观察的工作行为": "整理业务场景、功能需求及约束并形成需求记录", "对应任务ID": "T-JOB016-01;T-JOB032-01;T-JOB045-01", "来源岗位ID": "JOB016;JOB032;JOB045", "摘要支持任务ID": "T-JOB016-01;T-JOB032-01;T-JOB045-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "限定系统需求；市场需求调研或一般分析不能自动归入系统需求", "人工审核状态": "待人工审核", "原三级能力编码": "C411", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "识别实体联系并完成E-R设计与关系模式转换", "课程尚未明确覆盖的工作行为": "系统业务场景、功能约束的完整需求梳理及需求记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N412", "父编码": "N41", "能力层级": "三级", "能力名称": "开发数据库业务应用", "可观察的工作行为": "围绕业务数据实现应用功能，展示实现结果", "对应任务ID": "T-JOB049-02;T-JOB050-01", "来源岗位ID": "JOB049;JOB050", "摘要支持任务ID": "T-JOB050-01", "研究推断任务ID": "T-JOB049-02", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留应用实现；开发报表不自动证明数据库业务应用开发，须人工复核", "人工审核状态": "待人工审核", "原三级能力编码": "C412", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N412", "父编码": "N41", "能力层级": "三级", "能力名称": "开发数据库业务应用", "可观察的工作行为": "围绕业务数据实现应用功能，展示实现结果", "对应任务ID": "T-JOB049-02;T-JOB050-01", "来源岗位ID": "JOB049;JOB050", "摘要支持任务ID": "T-JOB050-01", "研究推断任务ID": "T-JOB049-02", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留应用实现；开发报表不自动证明数据库业务应用开发，须人工复核", "人工审核状态": "待人工审核", "原三级能力编码": "C412", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "库表DDL、数据记录操作与查询等应用数据层操作", "课程尚未明确覆盖的工作行为": "应用功能实现和可运行业务应用成果；未明确程序连接及端到端业务实现", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N421", "父编码": "N42", "能力层级": "三级", "能力名称": "测试业务系统功能", "可观察的工作行为": "记录功能测试对象、过程与结果", "对应任务ID": "T-JOB008-02;T-JOB017-01", "来源岗位ID": "JOB008;JOB017", "摘要支持任务ID": "T-JOB008-02", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "测试与部署升级的交付物不同，单独评价", "人工审核状态": "待人工审核", "原三级能力编码": "C431", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N421", "父编码": "N42", "能力层级": "三级", "能力名称": "测试业务系统功能", "可观察的工作行为": "记录功能测试对象、过程与结果", "对应任务ID": "T-JOB008-02;T-JOB017-01", "来源岗位ID": "JOB008;JOB017", "摘要支持任务ID": "T-JOB008-02", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "测试与部署升级的交付物不同，单独评价", "人工审核状态": "待人工审核", "原三级能力编码": "C431", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见业务系统功能测试方法；SQL运行练习不是软件功能测试", "课程尚未明确覆盖的工作行为": "功能测试对象、测试过程及测试结果记录", "未见支撑建议分类": "其他专业课程可能承担", "分类理由": "系统测试可能由软件测试或项目课程讨论，未检查具体课程标准", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N422", "父编码": "N42", "能力层级": "三级", "能力名称": "部署与升级业务系统", "可观察的工作行为": "记录系统上线或升级的对象、步骤和结果", "对应任务ID": "T-JOB008-02;T-JOB017-01;T-JOB021-03;T-JOB032-01", "来源岗位ID": "JOB008;JOB017;JOB021;JOB032", "摘要支持任务ID": "T-JOB008-02;T-JOB021-03;T-JOB032-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "只有项目实施等泛词时不推定部署；不补写发布技术", "人工审核状态": "待人工审核", "原三级能力编码": "C431", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N422", "父编码": "N42", "能力层级": "三级", "能力名称": "部署与升级业务系统", "可观察的工作行为": "记录系统上线或升级的对象、步骤和结果", "对应任务ID": "T-JOB008-02;T-JOB017-01;T-JOB021-03;T-JOB032-01", "来源岗位ID": "JOB008;JOB017;JOB021;JOB032", "摘要支持任务ID": "T-JOB008-02;T-JOB021-03;T-JOB032-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "只有项目实施等泛词时不推定部署；不补写发布技术", "人工审核状态": "待人工审核", "原三级能力编码": "C431", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "MySQL安装部署及基本连接", "课程尚未明确覆盖的工作行为": "旅游业务系统上线、升级对象及完整步骤和结果记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N511", "父编码": "N51", "能力层级": "三级", "能力名称": "开展旅游业务调研", "可观察的工作行为": "围绕游客、市场或业务问题形成调查记录", "对应任务ID": "T-JOB007-02;T-JOB014-01;T-JOB028-01", "来源岗位ID": "JOB007;JOB014;JOB028", "摘要支持任务ID": "T-JOB007-02;T-JOB014-01;T-JOB028-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留行业调研任务，不强行加入数据库课程核心", "人工审核状态": "待人工审核", "原三级能力编码": "C511", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N511", "父编码": "N51", "能力层级": "三级", "能力名称": "开展旅游业务调研", "可观察的工作行为": "围绕游客、市场或业务问题形成调查记录", "对应任务ID": "T-JOB007-02;T-JOB014-01;T-JOB028-01", "来源岗位ID": "JOB007;JOB014;JOB028", "摘要支持任务ID": "T-JOB007-02;T-JOB014-01;T-JOB028-01", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留行业调研任务，不强行加入数据库课程核心", "人工审核状态": "待人工审核", "原三级能力编码": "C511", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见游客市场或业务调查任务", "课程尚未明确覆盖的工作行为": "确定调研问题、执行调查及形成调研记录", "未见支撑建议分类": "旅游业务背景能力", "分类理由": "游客市场调研属于行业业务背景，不以数据库关键词强配", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N512", "父编码": "N51", "能力层级": "三级", "能力名称": "协调业务与数据支持", "可观察的工作行为": "明确协作对象和需求，记录支持结果", "对应任务ID": "T-JOB004-01;T-JOB012-02;T-JOB017-01;T-JOB041-01", "来源岗位ID": "JOB004;JOB012;JOB017;JOB041", "摘要支持任务ID": "T-JOB004-01;T-JOB012-02;T-JOB041-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "项目实施不必然意味着沟通协作；要求对象或支持行为", "人工审核状态": "待人工审核", "原三级能力编码": "C512", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N512", "父编码": "N51", "能力层级": "三级", "能力名称": "协调业务与数据支持", "可观察的工作行为": "明确协作对象和需求，记录支持结果", "对应任务ID": "T-JOB004-01;T-JOB012-02;T-JOB017-01;T-JOB041-01", "来源岗位ID": "JOB004;JOB012;JOB017;JOB041", "摘要支持任务ID": "T-JOB004-01;T-JOB012-02;T-JOB041-01", "研究推断任务ID": "T-JOB017-01", "证据类型": "岗位摘要支持；研究推断", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "项目实施不必然意味着沟通协作；要求对象或支持行为", "人工审核状态": "待人工审核", "原三级能力编码": "C512", "摘要支持岗位数（含疑似重复）": 3, "摘要支持任务数": 3, "研究推断关联岗位数（非频次）": 1, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "素质目标层提出团队协作意识", "课程尚未明确覆盖的工作行为": "跨部门需求沟通、业务数据支持过程及支持结果记录", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N521", "父编码": "N52", "能力层级": "三级", "能力名称": "编制与维护技术文档", "可观察的工作行为": "记录系统或操作说明并形成可检查文档", "对应任务ID": "T-JOB021-03", "来源岗位ID": "JOB021", "摘要支持任务ID": "T-JOB021-03", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "与流程优化分开；不能把流程一词视为已经编写文档", "人工审核状态": "待人工审核", "原三级能力编码": "C521", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N521", "父编码": "N52", "能力层级": "三级", "能力名称": "编制与维护技术文档", "可观察的工作行为": "记录系统或操作说明并形成可检查文档", "对应任务ID": "T-JOB021-03", "来源岗位ID": "JOB021", "摘要支持任务ID": "T-JOB021-03", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "与流程优化分开；不能把流程一词视为已经编写文档", "人工审核状态": "待人工审核", "原三级能力编码": "C521", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见系统或操作技术说明文档编制要求", "课程尚未明确覆盖的工作行为": "编制和维护技术说明、操作记录或系统文档", "未见支撑建议分类": "本课程潜在改进方向", "分类理由": "可讨论数据库操作文档交付，不能反写为现行要求", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N522", "父编码": "N52", "能力层级": "三级", "能力名称": "梳理数据处理流程", "可观察的工作行为": "说明数据处理步骤及前后衔接关系并形成流程说明", "对应任务ID": "T-JOB001-04", "来源岗位ID": "JOB001", "摘要支持任务ID": "T-JOB001-04", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "流程梳理与文档维护分开，具体流程评价表述是研究拟定", "人工审核状态": "待人工审核", "原三级能力编码": "C521", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N522", "父编码": "N52", "能力层级": "三级", "能力名称": "梳理数据处理流程", "可观察的工作行为": "说明数据处理步骤及前后衔接关系并形成流程说明", "对应任务ID": "T-JOB001-04", "来源岗位ID": "JOB001", "摘要支持任务ID": "T-JOB001-04", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "B数据库课程延伸相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "流程梳理与文档维护分开，具体流程评价表述是研究拟定", "人工审核状态": "待人工审核", "原三级能力编码": "C521", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "SQL操作顺序和事务逻辑等操作流程基础", "课程尚未明确覆盖的工作行为": "数据处理步骤的完整梳理、衔接关系及流程说明产出", "未见支撑建议分类": "不适用（本项非未见明确支撑）", "分类理由": "仅对未见明确支撑项分类；其余仍说明未覆盖行为", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "部分支撑"}</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr"/>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>{"新编码": "N531", "父编码": "N53", "能力层级": "三级", "能力名称": "跟进游客服务整改", "可观察的工作行为": "记录服务问题、整改进度与处理结果", "对应任务ID": "T-JOB014-03", "来源岗位ID": "JOB014", "摘要支持任务ID": "T-JOB014-03", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留行业服务背景，不推断数据库技能", "人工审核状态": "待人工审核", "原三级能力编码": "C531", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准"}</t>
+          <t>{"新编码": "N531", "父编码": "N53", "能力层级": "三级", "能力名称": "跟进游客服务整改", "可观察的工作行为": "记录服务问题、整改进度与处理结果", "对应任务ID": "T-JOB014-03", "来源岗位ID": "JOB014", "摘要支持任务ID": "T-JOB014-03", "研究推断任务ID": null, "证据类型": "岗位摘要支持", "证据状态": "全部待核验；无招聘原文明示证据", "课程适配类别": "C旅游行业背景相关", "适配判断边界": "研究判断，不等同于课程标准已覆盖；上位混合类别不能代替逐叶判断", "优化理由": "保留行业服务背景，不推断数据库技能", "人工审核状态": "待人工审核", "原三级能力编码": "C531", "摘要支持岗位数（含疑似重复）": 1, "摘要支持任务数": 1, "研究推断关联岗位数（非频次）": 0, "已核验招聘原文岗位数": 0, "招聘需求频次": "不计算正式需求频次；摘要候选数另列", "能力来源": "岗位任务归纳建议（AI辅助研究提出）", "行为指标来源": "研究拟定的可观察评价表述；不是招聘原文或课程标准", "课程支撑的具体技术行为": "未见游客服务整改任务", "课程尚未明确覆盖的工作行为": "服务问题记录、整改进度跟踪和处理结果记录", "未见支撑建议分类": "旅游业务背景能力", "分类理由": "游客服务整改属于行业业务流程背景", "分类性质": "研究建议，非课程标准证明，也非已核实的其他课程承担事实", "课程支撑等级": "未见明确支撑"}</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr"/>
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>岗位全部待核验，课程匹配及图谱语义联系全部待人工审核；文本支撑不等同实际培养</t>
+          <t>历史招聘及关系证据状态保留但不再新增核验任务；当前仅课程能力图谱复核，文本支撑不等同实际培养</t>
         </is>
       </c>
     </row>
